--- a/outputs/36191.xlsx
+++ b/outputs/36191.xlsx
@@ -110,8 +110,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -307,44 +311,44 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="43.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <f aca="false">C8</f>
         <v>0</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="0" t="str">
+      <c r="C2" s="1" t="str">
         <f aca="false">LEFT(B2,FIND(" ",B2,FIND(" ",B2)+1)-1)</f>
         <v>Sharon Smith</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="str">
+      <c r="A3" s="1" t="str">
         <f aca="false">LEFT(B3,FIND(" ",B3)-1)</f>
         <v>Sam</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="0" t="str">
+      <c r="C3" s="1" t="str">
         <f aca="false">LEFT(B3,FIND(" ",B3,FIND(" ",B3)+1)-1)</f>
         <v>Sam Landon</v>
       </c>

--- a/outputs/36191.xlsx
+++ b/outputs/36191.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t xml:space="preserve">Sharon Smith sharon.smith@BTRcom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sharon Smith</t>
   </si>
   <si>
     <t xml:space="preserve">Sam Landon sam@BTR.com</t>
@@ -335,9 +338,8 @@
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="str">
-        <f aca="false">LEFT(B2,FIND(" ",B2,FIND(" ",B2)+1)-1)</f>
-        <v>Sharon Smith</v>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -346,11 +348,11 @@
         <v>Sam</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="str">
-        <f aca="false">LEFT(B3,FIND(" ",B3,FIND(" ",B3)+1)-1)</f>
-        <v>Sam Landon</v>
+        <f aca="false">LEFT(B3,FIND(" ",B3,2)-1)</f>
+        <v>Sam</v>
       </c>
     </row>
   </sheetData>
